--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -957,17 +957,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1045,15 +1045,15 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1109,24 +1109,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       <c r="I11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>▼ 25,0%</t>
         </is>
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1395,9 +1395,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1468,13 +1468,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1547,24 +1547,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1622,9 +1622,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1687,17 +1687,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1985,24 +1985,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2060,9 +2060,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2204,11 +2204,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
@@ -2281,20 +2281,20 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2344,9 +2344,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2423,24 +2423,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2498,9 +2498,9 @@
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2509,11 +2509,11 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2563,17 +2563,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2642,11 +2642,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2861,24 +2861,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2936,9 +2936,9 @@
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3001,17 +3001,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>3</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3301,22 +3301,22 @@
       <c r="I39" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3366,15 +3366,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3439,17 +3439,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3527,20 +3527,20 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3666,9 +3666,9 @@
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3804,17 +3804,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3956,24 +3956,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,20 +4020,20 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,25 +4166,25 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4317,20 +4317,20 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4393,51 +4393,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4462,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4505,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4544,7 +4540,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4578,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4608,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4651,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4692,9 +4688,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4724,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4754,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4797,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4827,7 +4823,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4835,8 +4831,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>2</v>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4845,37 +4843,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4909,24 +4909,24 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4943,12 +4943,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4976,17 +4976,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5049,17 +5049,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5128,24 +5128,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5162,12 +5162,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5192,20 +5192,20 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5214,11 +5214,11 @@
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5308,12 +5308,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5347,24 +5347,24 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5414,15 +5414,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5454,12 +5454,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5487,17 +5487,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5566,24 +5566,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5600,12 +5600,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5639,24 +5639,24 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5706,13 +5706,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5746,12 +5746,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5779,17 +5779,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5871,11 +5871,11 @@
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5922,33 +5922,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5965,12 +5965,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6038,78 +6038,516 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-002</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Cabide Transparente</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>4353289878</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="n">
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>12,5%</t>
         </is>
       </c>
-      <c r="L77" s="2" t="n">
+      <c r="L83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -589,12 +589,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -602,20 +602,20 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -673,9 +673,9 @@
       <c r="I3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -753,15 +753,15 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -957,17 +957,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,24 +1182,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1255,24 +1255,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1395,17 +1395,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1622,9 +1622,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1693,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1906,17 +1906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2049,16 +2049,16 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2071,11 +2071,11 @@
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2125,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2206,9 +2206,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2217,11 +2217,11 @@
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2344,17 +2344,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▲ 250,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2487,20 +2487,20 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2509,11 +2509,11 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2569,24 +2569,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2642,24 +2642,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2861,11 +2861,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3001,17 +3001,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3082,9 +3082,9 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3226,11 +3226,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3372,11 +3372,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3447,22 +3447,22 @@
       <c r="I41" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3591,11 +3591,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3804,17 +3804,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3877,17 +3877,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4102,24 +4102,24 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4166,25 +4166,25 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4321,16 +4321,16 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4461,22 +4461,22 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4604,25 +4604,25 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>6</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4750,25 +4750,25 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4831,10 +4831,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4843,41 +4841,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4900,7 +4896,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4909,24 +4905,24 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4943,14 +4939,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4973,7 +4969,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4981,8 +4977,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -4991,39 +4989,41 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5049,17 +5049,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5089,14 +5089,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5130,9 +5130,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5162,14 +5162,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5192,33 +5192,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5235,14 +5235,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5274,11 +5274,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5308,14 +5308,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5338,20 +5338,20 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5360,11 +5360,11 @@
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5381,14 +5381,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5414,17 +5414,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5454,14 +5454,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5484,33 +5484,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5527,14 +5527,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5557,33 +5557,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5600,14 +5600,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5630,33 +5630,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5673,14 +5673,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5721,15 +5721,15 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5746,14 +5746,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5785,24 +5785,24 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5819,14 +5819,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5860,9 +5860,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5933,9 +5933,9 @@
       <c r="I75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5965,14 +5965,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6004,11 +6004,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6038,14 +6038,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6077,11 +6077,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6111,14 +6111,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6144,9 +6144,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6184,14 +6184,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6217,17 +6217,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6257,14 +6257,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6287,20 +6287,20 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6309,11 +6309,11 @@
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6330,14 +6330,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6360,33 +6360,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6403,14 +6403,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6442,24 +6442,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6476,14 +6476,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6511,20 +6511,20 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6546,8 +6546,154 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -753,15 +753,15 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -892,9 +892,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1255,24 +1255,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1330,9 +1330,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1629,15 +1629,15 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1693,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1979,17 +1979,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2052,13 +2052,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2206,9 +2206,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2217,11 +2217,11 @@
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2271,17 +2271,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2350,11 +2350,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2569,24 +2569,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2644,9 +2644,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2709,17 +2709,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2928,9 +2928,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3007,24 +3007,24 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3082,9 +3082,9 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3147,17 +3147,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3226,11 +3226,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3445,24 +3445,24 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3520,9 +3520,9 @@
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3585,17 +3585,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>3</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3664,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       <c r="I47" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3950,9 +3950,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4023,17 +4023,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4111,20 +4111,20 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4250,9 +4250,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4388,17 +4388,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4540,24 +4540,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,25 +4750,25 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>8</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4901,20 +4901,20 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4977,51 +4977,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5046,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5089,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5128,7 +5124,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5162,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5192,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5235,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5276,9 +5272,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5308,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5338,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5381,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5411,7 +5407,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5419,8 +5415,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>2</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5429,37 +5427,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5493,24 +5493,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5560,17 +5560,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5600,12 +5600,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5639,11 +5639,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5712,24 +5712,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5776,20 +5776,20 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5798,11 +5798,11 @@
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5892,12 +5892,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5931,24 +5931,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5965,12 +5965,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5998,9 +5998,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
@@ -6038,12 +6038,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6071,9 +6071,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6150,24 +6150,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6223,24 +6223,24 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6290,13 +6290,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6330,12 +6330,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6363,17 +6363,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6403,12 +6403,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6455,11 +6455,11 @@
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6506,33 +6506,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>4</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6622,78 +6622,516 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-002</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Cabide Transparente</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>4353289878</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>12,5%</t>
         </is>
       </c>
-      <c r="L85" s="2" t="n">
+      <c r="L91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,20 +808,20 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -830,11 +830,11 @@
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1030,17 +1030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1109,24 +1109,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1191,15 +1191,15 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1330,9 +1330,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1693,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1768,9 +1768,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1906,17 +1906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2067,15 +2067,15 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2350,11 +2350,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2417,17 +2417,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2490,13 +2490,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2569,24 +2569,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2644,9 +2644,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2655,11 +2655,11 @@
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2709,17 +2709,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3007,24 +3007,24 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3082,9 +3082,9 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3147,17 +3147,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3226,11 +3226,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3366,9 +3366,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3445,24 +3445,24 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3520,9 +3520,9 @@
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3531,11 +3531,11 @@
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3585,17 +3585,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3664,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3883,24 +3883,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3958,9 +3958,9 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4023,17 +4023,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>3</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4323,22 +4323,22 @@
       <c r="I53" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4388,9 +4388,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4461,17 +4461,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4549,20 +4549,20 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4688,9 +4688,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4826,17 +4826,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4978,24 +4978,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5124,11 +5124,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,25 +5188,25 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>8</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5339,20 +5339,20 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5415,51 +5415,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5484,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5527,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5566,7 +5562,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5600,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5630,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5673,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5714,9 +5710,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5746,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5776,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5819,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5849,7 +5845,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5857,8 +5853,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>2</v>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5867,37 +5865,39 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5931,24 +5931,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5965,12 +5965,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5998,17 +5998,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6077,11 +6077,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6150,24 +6150,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6214,20 +6214,20 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6236,11 +6236,11 @@
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6330,12 +6330,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6369,24 +6369,24 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6403,12 +6403,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6436,9 +6436,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
@@ -6476,12 +6476,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6509,9 +6509,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6588,24 +6588,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6661,24 +6661,24 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6728,13 +6728,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6768,12 +6768,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6801,17 +6801,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6893,11 +6893,11 @@
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6944,33 +6944,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>4</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7060,78 +7060,516 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-002</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Cabide Transparente</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>4353289878</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>12,5%</t>
         </is>
       </c>
-      <c r="L91" s="2" t="n">
+      <c r="L97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -589,12 +589,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -607,15 +607,15 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -808,20 +808,20 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -830,11 +830,11 @@
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -954,25 +954,25 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1255,24 +1255,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1468,17 +1468,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -1624,20 +1624,20 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1695,9 +1695,9 @@
       <c r="I17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1775,15 +1775,15 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1906,17 +1906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1979,17 +1979,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2204,24 +2204,24 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2277,24 +2277,24 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2350,11 +2350,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2417,17 +2417,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2644,9 +2644,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2715,24 +2715,24 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2861,11 +2861,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2928,17 +2928,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3007,11 +3007,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3071,16 +3071,16 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3147,17 +3147,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3228,9 +3228,9 @@
       <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3239,11 +3239,11 @@
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3366,17 +3366,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3509,20 +3509,20 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3531,11 +3531,11 @@
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3591,24 +3591,24 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3664,24 +3664,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3883,11 +3883,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4023,17 +4023,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4104,9 +4104,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4469,22 +4469,22 @@
       <c r="I55" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4613,11 +4613,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4759,11 +4759,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4826,17 +4826,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4899,17 +4899,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4969,33 +4969,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,14 +5085,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5124,24 +5124,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5188,25 +5188,25 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,14 +5231,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5270,11 +5270,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,14 +5304,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5343,16 +5343,16 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -5377,14 +5377,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5416,11 +5416,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5450,14 +5450,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5483,22 +5483,22 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,14 +5523,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5562,11 +5562,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,14 +5596,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5626,25 +5626,25 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,14 +5669,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5742,14 +5742,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5772,25 +5772,25 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,14 +5815,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5853,10 +5853,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5865,41 +5863,39 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5922,7 +5918,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5931,24 +5927,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5965,14 +5961,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5995,7 +5991,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6003,8 +5999,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6013,39 +6011,41 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6071,17 +6071,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6111,14 +6111,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6152,9 +6152,9 @@
       <c r="I78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6184,14 +6184,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6214,33 +6214,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6257,14 +6257,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6296,11 +6296,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6330,14 +6330,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6360,20 +6360,20 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6382,11 +6382,11 @@
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6403,14 +6403,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6436,17 +6436,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6476,14 +6476,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6506,33 +6506,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6549,14 +6549,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6579,33 +6579,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6622,14 +6622,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6652,33 +6652,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6695,14 +6695,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6743,15 +6743,15 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6768,14 +6768,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6807,24 +6807,24 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6841,14 +6841,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6882,9 +6882,9 @@
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6955,9 +6955,9 @@
       <c r="I89" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6987,14 +6987,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7026,11 +7026,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7060,14 +7060,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7099,11 +7099,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7133,14 +7133,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7166,9 +7166,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7206,14 +7206,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7239,17 +7239,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7279,14 +7279,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7309,20 +7309,20 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7331,11 +7331,11 @@
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7352,14 +7352,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7382,33 +7382,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>2</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7425,14 +7425,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7464,24 +7464,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7498,14 +7498,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7533,20 +7533,20 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
@@ -7568,8 +7568,154 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,17 +811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -892,9 +892,9 @@
       <c r="I6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,25 +954,25 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,25 +1246,25 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1337,15 +1337,15 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1476,7 +1476,7 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1547,24 +1547,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1906,17 +1906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2125,15 +2125,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>▲ 200,0%</t>
         </is>
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2213,15 +2213,15 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2279,22 +2279,22 @@
       <c r="I25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2344,15 +2344,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2417,9 +2417,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2505,15 +2505,15 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 70,00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2644,9 +2644,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2715,24 +2715,24 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2934,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3007,24 +3007,24 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3074,17 +3074,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3226,11 +3226,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3239,11 +3239,11 @@
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3293,17 +3293,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3366,17 +3366,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 250,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -3677,11 +3677,11 @@
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3804,9 +3804,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3883,24 +3883,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3956,24 +3956,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4029,11 +4029,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4169,17 +4169,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,16 +4458,16 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4476,15 +4476,15 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>3</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4759,24 +4759,24 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4834,9 +4834,9 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4972,17 +4972,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5045,17 +5045,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5133,15 +5133,15 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5264,15 +5264,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5425,15 +5425,15 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,25 +5480,25 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5629,22 +5629,22 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,25 +5772,25 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>5</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5856,9 +5856,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5921,22 +5921,22 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -5999,10 +5999,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I76" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6011,39 +6009,37 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6068,33 +6064,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>10</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6111,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6184,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6214,33 +6210,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6257,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6287,7 +6283,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6295,47 +6291,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6360,33 +6360,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6403,12 +6403,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6476,12 +6476,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6506,33 +6506,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6582,15 +6582,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -6622,12 +6622,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6652,33 +6652,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6743,15 +6743,15 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6768,12 +6768,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6809,7 +6809,7 @@
       <c r="I87" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
+      <c r="J87" s="4" t="inlineStr">
         <is>
           <t>▼ 25,0%</t>
         </is>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6874,17 +6874,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6947,17 +6947,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7026,24 +7026,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7099,24 +7099,24 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7133,12 +7133,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7172,11 +7172,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7279,12 +7279,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7312,17 +7312,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7352,12 +7352,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7385,15 +7385,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
         <is>
           <t>▲ 100,0%</t>
         </is>
@@ -7425,12 +7425,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7464,11 +7464,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7477,11 +7477,11 @@
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7528,33 +7528,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
-        </is>
-      </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7604,9 +7604,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
@@ -7644,78 +7644,370 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-002</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Cabide Transparente</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>4353289878</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="n">
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>12,5%</t>
         </is>
       </c>
-      <c r="L99" s="2" t="n">
+      <c r="L103" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="M103" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -965,22 +965,22 @@
       <c r="I7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,55 +1173,59 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1250,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>▲ 100,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1323,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,7 +1332,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1337,15 +1341,15 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1396,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1439,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1476,7 +1480,7 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1508,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1542,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1585,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,11 +1624,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1688,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1697,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1766,11 +1770,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1833,17 +1837,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1877,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1906,9 +1910,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -1946,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,7 +1980,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1985,24 +1989,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2023,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,7 +2053,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2067,15 +2071,15 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2096,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2135,7 +2139,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,7 +2199,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2203,8 +2207,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2213,37 +2219,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2271,17 +2279,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2319,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2344,17 +2352,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2422,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2465,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,7 +2495,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2496,24 +2504,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2538,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2568,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2611,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2636,17 +2644,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2684,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,7 +2714,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2715,24 +2723,24 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2757,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,7 +2787,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2788,24 +2796,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2830,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2855,17 +2863,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,12 +2903,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2928,17 +2936,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2976,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,25 +3006,25 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
@@ -3024,7 +3032,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3049,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,7 +3079,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3080,24 +3088,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3122,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3152,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3195,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3226,11 +3234,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3268,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,7 +3298,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3299,24 +3307,24 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3341,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3366,13 +3374,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3406,12 +3414,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3445,11 +3453,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,12 +3487,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,7 +3517,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3520,9 +3528,9 @@
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3531,11 +3539,11 @@
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3560,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3585,17 +3593,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,12 +3633,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3658,17 +3666,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3706,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3736,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3779,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,12 +3809,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
@@ -3819,15 +3827,15 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3852,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,7 +3882,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3883,24 +3891,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3925,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,7 +3955,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3958,9 +3966,9 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3969,11 +3977,11 @@
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3998,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4029,9 +4037,9 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>▼ 66,7%</t>
         </is>
@@ -4063,12 +4071,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4096,17 +4104,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4144,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4169,17 +4177,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4209,12 +4217,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,7 +4247,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4257,15 +4265,15 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4290,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,7 +4320,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4321,24 +4329,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4363,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4396,9 +4404,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4436,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4461,17 +4469,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4501,12 +4509,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4540,11 +4548,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4582,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,33 +4612,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4655,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4686,7 +4694,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4720,12 +4728,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,7 +4758,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4759,16 +4767,16 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
@@ -4793,12 +4801,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4834,7 +4842,7 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -4866,12 +4874,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4905,11 +4913,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>3</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4939,12 +4947,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4980,9 +4988,9 @@
       <c r="I62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5000,7 +5008,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5012,12 +5020,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5051,11 +5059,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5085,12 +5093,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5118,13 +5126,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5158,12 +5166,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5197,11 +5205,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5231,12 +5239,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5261,20 +5269,20 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5283,11 +5291,11 @@
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,12 +5312,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5337,17 +5345,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5377,12 +5385,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,7 +5415,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5416,24 +5424,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5458,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,33 +5488,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5531,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5556,17 +5564,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,12 +5604,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5631,20 +5639,20 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
@@ -5669,12 +5677,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5699,7 +5707,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5708,24 +5716,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,12 +5750,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,33 +5780,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5823,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5854,11 +5862,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,12 +5896,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,12 +5926,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
@@ -5931,20 +5939,20 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5969,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6034,12 +6042,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,33 +6072,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6115,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6180,12 +6188,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,33 +6218,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,12 +6261,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6283,7 +6291,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6291,51 +6299,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6360,33 +6364,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6403,12 +6407,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6442,7 +6446,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6476,12 +6480,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6506,16 +6510,16 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6524,15 +6528,15 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6549,12 +6553,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6590,7 +6594,7 @@
       <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="4" t="inlineStr">
+      <c r="J84" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -6622,12 +6626,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6652,33 +6656,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6695,12 +6699,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6756,7 +6760,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6768,12 +6772,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6798,7 +6802,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6807,24 +6811,24 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6841,12 +6845,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6874,17 +6878,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6914,12 +6918,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6947,15 +6951,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J89" s="3" t="inlineStr">
+      <c r="J89" s="4" t="inlineStr">
         <is>
           <t>▲ 33,3%</t>
         </is>
@@ -6987,12 +6991,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7017,33 +7021,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7060,12 +7064,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7090,33 +7094,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7133,12 +7137,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7163,7 +7167,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7172,7 +7176,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7181,15 +7185,15 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7206,12 +7210,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7236,33 +7240,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7279,12 +7283,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7320,7 +7324,7 @@
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="4" t="inlineStr">
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -7352,12 +7356,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7382,33 +7386,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7425,12 +7429,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7468,7 +7472,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7498,12 +7502,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7528,33 +7532,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7571,12 +7575,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7604,17 +7608,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7644,12 +7648,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7674,33 +7678,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7717,12 +7721,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7747,7 +7751,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7756,11 +7760,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7769,11 +7773,11 @@
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7790,12 +7794,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7820,25 +7824,25 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>10</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
@@ -7863,12 +7867,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7902,7 +7906,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -7936,12 +7940,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7975,16 +7979,16 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
@@ -7992,22 +7996,1778 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 74,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -817,24 +817,24 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1181,51 +1181,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1250,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 186,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 402,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1293,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1326,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1366,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1396,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 37,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1439,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1469,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 37,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1478,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1542,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1585,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1626,9 +1622,9 @@
       <c r="I16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1658,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1688,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1697,24 +1693,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1804,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1837,17 +1833,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1877,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1916,7 +1912,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1950,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1980,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1989,24 +1985,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2023,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2062,7 +2058,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2096,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2129,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2246,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2276,33 +2272,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2319,12 +2315,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2392,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2422,7 +2418,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2431,24 +2427,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2465,12 +2461,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2538,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2571,17 +2567,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2611,12 +2607,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2644,17 +2640,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2684,12 +2680,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2714,7 +2710,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2723,24 +2719,24 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2757,12 +2753,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2787,7 +2783,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2796,7 +2792,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2805,15 +2801,15 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2830,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2863,13 +2859,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2903,12 +2899,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2936,17 +2932,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,12 +2972,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3006,20 +3002,20 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3028,11 +3024,11 @@
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3049,12 +3045,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3079,7 +3075,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3087,8 +3083,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>1</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3097,37 +3095,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3152,33 +3152,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3233,47 +3233,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3298,7 +3302,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3307,24 +3311,24 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3341,12 +3345,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3371,7 +3375,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3379,8 +3383,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>2</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3389,37 +3395,39 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3453,11 +3461,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3487,12 +3495,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3517,7 +3525,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3525,47 +3533,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3599,11 +3611,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3633,12 +3645,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3666,17 +3678,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3706,12 +3718,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3739,17 +3751,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3779,12 +3791,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3809,7 +3821,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3818,7 +3830,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3827,15 +3839,15 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3852,12 +3864,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3882,7 +3894,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3891,24 +3903,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3925,12 +3937,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3998,12 +4010,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4037,11 +4049,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4071,12 +4083,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4104,17 +4116,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4144,12 +4156,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4177,17 +4189,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4217,12 +4229,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4247,7 +4259,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4255,8 +4267,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>1</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4265,37 +4279,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4320,7 +4336,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4329,24 +4345,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4363,12 +4379,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4404,9 +4420,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4436,12 +4452,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4475,11 +4491,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4509,12 +4525,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4548,11 +4564,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4582,12 +4598,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4621,11 +4637,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4655,12 +4671,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4694,11 +4710,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4728,12 +4744,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4758,7 +4774,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4767,16 +4783,16 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
@@ -4801,12 +4817,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4840,11 +4856,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4874,12 +4890,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4907,17 +4923,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4947,12 +4963,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4986,11 +5002,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5020,12 +5036,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5050,7 +5066,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5061,22 +5077,22 @@
       <c r="I63" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5093,12 +5109,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5126,9 +5142,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
@@ -5166,12 +5182,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5205,11 +5221,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5239,12 +5255,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5269,7 +5285,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5277,8 +5293,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5287,37 +5305,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5351,11 +5371,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5385,12 +5405,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5426,9 +5446,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5458,12 +5478,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5488,25 +5508,25 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
@@ -5514,7 +5534,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5531,12 +5551,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5564,17 +5584,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5604,12 +5624,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5634,33 +5654,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5677,12 +5697,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5707,20 +5727,20 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5729,11 +5749,11 @@
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5750,12 +5770,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5780,7 +5800,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5789,24 +5809,24 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5823,12 +5843,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5853,7 +5873,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5862,24 +5882,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5896,12 +5916,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5929,17 +5949,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5969,12 +5989,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6002,17 +6022,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6042,12 +6062,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6072,20 +6092,20 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6094,11 +6114,11 @@
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6115,12 +6135,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6145,7 +6165,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6154,7 +6174,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6163,15 +6183,15 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6188,12 +6208,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6218,33 +6238,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6261,12 +6281,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6334,12 +6354,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6364,33 +6384,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6407,12 +6427,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6446,7 +6466,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6480,12 +6500,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6510,7 +6530,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6519,24 +6539,24 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6553,12 +6573,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6626,12 +6646,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6665,11 +6685,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6699,12 +6719,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6732,17 +6752,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6760,7 +6780,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6772,12 +6792,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6811,11 +6831,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6845,12 +6865,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6875,7 +6895,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6884,7 +6904,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -6893,15 +6913,15 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6918,12 +6938,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6957,11 +6977,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6991,12 +7011,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7024,17 +7044,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7064,12 +7084,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7097,17 +7117,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7137,12 +7157,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7167,33 +7187,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7210,12 +7230,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7240,33 +7260,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7283,12 +7303,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7313,7 +7333,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7322,24 +7342,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7356,12 +7376,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7386,33 +7406,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7429,12 +7449,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7468,11 +7488,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7502,12 +7522,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7532,33 +7552,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7575,12 +7595,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7614,11 +7634,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7648,12 +7668,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7678,33 +7698,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7721,12 +7741,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7760,7 +7780,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -7794,12 +7814,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7824,25 +7844,25 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
@@ -7850,7 +7870,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7867,12 +7887,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7908,9 +7928,9 @@
       <c r="I102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7940,12 +7960,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7970,7 +7990,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -7979,24 +7999,24 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8013,12 +8033,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8043,7 +8063,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8051,51 +8071,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8129,11 +8145,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8163,12 +8179,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8196,13 +8212,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8236,12 +8252,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8269,13 +8285,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8309,12 +8325,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8339,7 +8355,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8350,9 +8366,9 @@
       <c r="I108" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8361,11 +8377,11 @@
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8382,12 +8398,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8412,33 +8428,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8455,12 +8471,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8494,11 +8510,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8528,12 +8544,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8558,20 +8574,20 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8580,11 +8596,11 @@
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8601,12 +8617,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8640,11 +8656,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8674,12 +8690,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8704,33 +8720,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8747,12 +8763,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8786,16 +8802,16 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
@@ -8803,7 +8819,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8820,12 +8836,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8850,7 +8866,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -8859,24 +8875,24 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8893,12 +8909,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8932,11 +8948,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8966,12 +8982,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9005,11 +9021,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9039,12 +9055,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9078,11 +9094,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9112,12 +9128,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9151,11 +9167,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9185,12 +9201,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9224,11 +9240,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9258,12 +9274,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9291,13 +9307,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9331,12 +9347,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9364,17 +9380,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9404,12 +9420,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9434,33 +9450,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>66,7%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9477,12 +9493,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9507,7 +9523,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9516,11 +9532,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9529,11 +9545,11 @@
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9550,12 +9566,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9585,20 +9601,20 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
-        </is>
-      </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
@@ -9606,7 +9622,7 @@
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9623,12 +9639,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9662,11 +9678,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9696,78 +9712,3148 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-002</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Cabide Transparente</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>4353289878</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="n">
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
         <is>
           <t>12,5%</t>
         </is>
       </c>
-      <c r="L127" s="2" t="n">
+      <c r="L169" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M127" s="2" t="inlineStr">
+      <c r="M169" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N127" s="2" t="inlineStr">
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,8 +597,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -607,39 +609,41 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -662,33 +666,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 37,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -746,9 +750,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +782,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -813,20 +817,20 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 76,9%</t>
+        <v>16</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -851,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -890,11 +894,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +928,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -954,7 +958,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 74,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -963,24 +967,24 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 85,7%</t>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1036,7 +1040,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1070,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1103,17 +1107,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1184,9 +1188,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1220,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1246,33 +1250,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 186,00</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 402,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1322,17 +1326,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,14 +1366,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1392,33 +1396,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 37,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,5%</t>
+          <t>R$ 186,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 402,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1465,33 +1469,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 37,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1512,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1538,25 +1542,25 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 37,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
@@ -1564,7 +1568,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1585,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1611,7 +1615,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 37,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,24 +1624,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1658,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1697,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1731,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1766,11 +1770,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,14 +1804,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1839,11 +1843,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1877,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1946,14 +1950,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1985,11 +1989,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2023,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2062,7 +2066,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,14 +2096,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2125,9 +2129,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
@@ -2135,7 +2139,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,14 +2169,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2195,7 +2199,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2203,10 +2207,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2215,41 +2217,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2272,20 +2272,20 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2294,11 +2294,11 @@
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2315,14 +2315,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2353,8 +2353,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2363,39 +2365,41 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2418,7 +2422,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2427,11 +2431,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2440,11 +2444,11 @@
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2461,14 +2465,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2502,9 +2506,9 @@
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2534,14 +2538,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2573,11 +2577,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,14 +2611,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2646,11 +2650,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2680,14 +2684,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2719,11 +2723,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2753,14 +2757,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2792,11 +2796,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2826,14 +2830,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2865,11 +2869,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2899,12 +2903,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2942,7 +2946,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2972,14 +2976,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3011,7 +3015,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3045,14 +3049,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3075,7 +3079,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3083,10 +3087,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3095,39 +3097,37 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3345,12 +3345,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3572,12 +3572,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3645,14 +3645,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3683,8 +3683,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3693,39 +3695,41 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3751,17 +3755,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3791,12 +3795,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3864,14 +3868,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3894,33 +3898,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3937,12 +3941,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4010,14 +4014,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4040,7 +4044,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4049,24 +4053,24 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4083,12 +4087,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4156,14 +4160,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4195,11 +4199,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4229,14 +4233,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4259,7 +4263,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4267,10 +4271,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4279,41 +4281,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4345,11 +4345,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4379,14 +4379,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4417,8 +4417,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4427,39 +4429,41 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4491,11 +4495,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4525,14 +4529,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4566,9 +4570,9 @@
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4598,14 +4602,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4631,17 +4635,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4671,14 +4675,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4710,11 +4714,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4744,14 +4748,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4774,33 +4778,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4817,12 +4821,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4890,14 +4894,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4920,33 +4924,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4963,12 +4967,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5036,14 +5040,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5066,33 +5070,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5109,12 +5113,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5152,7 +5156,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5182,14 +5186,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5212,7 +5216,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5221,24 +5225,24 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5255,14 +5259,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5285,7 +5289,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5293,10 +5297,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5305,41 +5307,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5365,17 +5365,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5405,14 +5405,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5443,8 +5443,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5453,39 +5455,41 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5508,33 +5512,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5551,14 +5555,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5592,9 +5596,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5624,14 +5628,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5654,33 +5658,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5697,14 +5701,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5730,17 +5734,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5770,14 +5774,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5800,33 +5804,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5843,14 +5847,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5873,12 +5877,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
@@ -5891,15 +5895,15 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5916,14 +5920,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5946,33 +5950,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5989,14 +5993,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6019,33 +6023,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6062,14 +6066,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6092,20 +6096,20 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6114,11 +6118,11 @@
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6135,14 +6139,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6165,33 +6169,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6208,14 +6212,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6238,25 +6242,25 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
@@ -6264,7 +6268,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6281,14 +6285,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6311,7 +6315,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6320,24 +6324,24 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6354,14 +6358,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6389,20 +6393,20 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6427,14 +6431,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6466,11 +6470,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6500,14 +6504,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6530,7 +6534,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6539,24 +6543,24 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6573,14 +6577,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6612,11 +6616,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6646,14 +6650,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6685,11 +6689,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6719,14 +6723,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6752,17 +6756,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6792,14 +6796,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6831,11 +6835,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6865,14 +6869,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6895,12 +6899,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
@@ -6908,20 +6912,20 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6938,12 +6942,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6979,9 +6983,9 @@
       <c r="I89" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7011,14 +7015,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7041,7 +7045,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7050,7 +7054,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7059,15 +7063,15 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7084,14 +7088,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7123,11 +7127,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7157,14 +7161,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7190,17 +7194,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7230,14 +7234,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7263,17 +7267,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7303,14 +7307,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7333,33 +7337,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7376,14 +7380,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7406,33 +7410,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7449,14 +7453,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7479,7 +7483,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7488,24 +7492,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7522,14 +7526,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7552,7 +7556,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7561,24 +7565,24 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7595,14 +7599,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7634,11 +7638,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7668,14 +7672,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7701,17 +7705,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7741,14 +7745,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7780,7 +7784,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -7814,14 +7818,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7844,33 +7848,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7887,14 +7891,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7928,9 +7932,9 @@
       <c r="I102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7960,14 +7964,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7990,7 +7994,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -7999,24 +8003,24 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8033,14 +8037,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8072,11 +8076,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8106,14 +8110,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8145,11 +8149,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8179,14 +8183,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8212,17 +8216,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8252,14 +8256,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8291,11 +8295,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8325,14 +8329,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8355,16 +8359,16 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8377,11 +8381,11 @@
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8398,14 +8402,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8431,17 +8435,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8471,14 +8475,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8501,7 +8505,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8512,9 +8516,9 @@
       <c r="I110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8523,11 +8527,11 @@
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8544,14 +8548,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8574,33 +8578,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8617,14 +8621,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8650,17 +8654,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8690,14 +8694,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8720,33 +8724,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8763,14 +8767,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8793,20 +8797,20 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8815,11 +8819,11 @@
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8836,14 +8840,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8866,7 +8870,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -8875,24 +8879,24 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8909,14 +8913,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8939,7 +8943,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -8948,24 +8952,24 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8982,14 +8986,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9021,11 +9025,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9055,12 +9059,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9098,7 +9102,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9128,14 +9132,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9167,11 +9171,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9201,14 +9205,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9240,7 +9244,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -9274,14 +9278,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9307,17 +9311,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9347,14 +9351,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9388,9 +9392,9 @@
       <c r="I122" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9420,14 +9424,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9450,33 +9454,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9493,14 +9497,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9532,11 +9536,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9566,14 +9570,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9596,33 +9600,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9639,14 +9643,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9678,11 +9682,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9712,14 +9716,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9742,7 +9746,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9753,22 +9757,22 @@
       <c r="I127" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9785,14 +9789,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9824,11 +9828,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9846,7 +9850,7 @@
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
@@ -9858,14 +9862,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9897,11 +9901,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -9931,14 +9935,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9970,7 +9974,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -9992,7 +9996,7 @@
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
@@ -10004,14 +10008,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10043,11 +10047,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10077,14 +10081,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10110,17 +10114,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10150,14 +10154,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10183,17 +10187,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10223,14 +10227,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10253,33 +10257,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10296,14 +10300,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10326,33 +10330,33 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -10369,14 +10373,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10399,7 +10403,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10408,24 +10412,24 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10442,14 +10446,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10472,25 +10476,25 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
@@ -10498,7 +10502,7 @@
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10515,14 +10519,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10554,11 +10558,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10588,14 +10592,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10627,16 +10631,16 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
@@ -10661,14 +10665,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10700,11 +10704,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10734,14 +10738,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10767,22 +10771,22 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
@@ -10790,7 +10794,7 @@
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10807,14 +10811,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10846,11 +10850,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10880,14 +10884,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10910,25 +10914,25 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
@@ -10936,7 +10940,7 @@
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10953,14 +10957,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10992,7 +10996,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11026,14 +11030,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11056,25 +11060,25 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
@@ -11082,7 +11086,7 @@
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11099,14 +11103,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11129,7 +11133,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -11137,10 +11141,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -11149,41 +11151,39 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11215,24 +11215,24 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11249,14 +11249,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11279,7 +11279,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -11287,8 +11287,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" s="2" t="n">
-        <v>0</v>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11297,39 +11299,41 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11355,17 +11359,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11395,14 +11399,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11436,9 +11440,9 @@
       <c r="I150" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11468,14 +11472,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11498,33 +11502,33 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H151" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11541,14 +11545,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11580,11 +11584,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11614,14 +11618,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11644,20 +11648,20 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11666,11 +11670,11 @@
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11687,14 +11691,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11720,17 +11724,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11760,14 +11764,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11790,33 +11794,33 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -11833,14 +11837,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11863,33 +11867,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11906,14 +11910,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11936,33 +11940,33 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -11979,14 +11983,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12009,7 +12013,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -12018,7 +12022,7 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
@@ -12027,15 +12031,15 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12052,14 +12056,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12082,7 +12086,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12091,24 +12095,24 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12125,14 +12129,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12166,9 +12170,9 @@
       <c r="I160" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12198,12 +12202,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12239,9 +12243,9 @@
       <c r="I161" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12271,14 +12275,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12310,11 +12314,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12344,14 +12348,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12383,11 +12387,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12417,14 +12421,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12450,9 +12454,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
@@ -12460,7 +12464,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12490,14 +12494,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12523,17 +12527,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12563,14 +12567,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12593,20 +12597,20 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12615,11 +12619,11 @@
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12636,14 +12640,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12666,33 +12670,33 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>2</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12709,14 +12713,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12739,7 +12743,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -12748,24 +12752,24 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L168" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12782,14 +12786,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12817,20 +12821,20 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L169" s="2" t="n">
@@ -12852,8 +12856,154 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,10 +597,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -609,41 +607,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -669,13 +665,13 @@
           <t>R$ 37,00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -684,7 +680,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -692,7 +688,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -709,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -739,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +743,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,39 +755,41 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -812,33 +812,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 37,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -855,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -896,9 +896,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,14 +928,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -963,20 +963,20 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 76,9%</t>
+        <v>16</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -1001,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1040,11 +1040,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1074,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 74,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1113,24 +1113,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▲ 85,7%</t>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1147,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1220,14 +1220,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1253,17 +1253,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1293,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1334,9 +1334,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1366,14 +1366,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1396,33 +1396,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 186,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 402,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1439,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1472,17 +1472,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1512,14 +1512,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1542,33 +1542,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 37,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,5%</t>
+          <t>R$ 186,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 402,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1585,14 +1585,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1615,33 +1615,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 37,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1658,14 +1658,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1688,25 +1688,25 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 37,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,14 +1731,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 37,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1770,24 +1770,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1804,14 +1804,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1843,24 +1843,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1877,14 +1877,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1916,11 +1916,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1950,14 +1950,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1989,11 +1989,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2096,14 +2096,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2135,11 +2135,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2242,14 +2242,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2275,9 +2275,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2315,14 +2315,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2353,10 +2353,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2365,41 +2363,39 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2422,20 +2418,20 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2444,11 +2440,11 @@
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2465,14 +2461,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2495,7 +2491,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2503,8 +2499,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2513,39 +2511,41 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2577,11 +2577,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2590,11 +2590,11 @@
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2611,14 +2611,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2652,9 +2652,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2684,14 +2684,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2723,11 +2723,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2757,14 +2757,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2796,11 +2796,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2830,14 +2830,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2869,11 +2869,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2903,14 +2903,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,14 +2976,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3015,11 +3015,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3122,14 +3122,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3195,14 +3195,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3233,10 +3233,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I38" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3245,39 +3243,37 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3345,12 +3341,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3422,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3495,12 +3491,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3572,12 +3568,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3645,12 +3641,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3722,12 +3718,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3795,14 +3791,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3825,7 +3821,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3833,8 +3829,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3843,39 +3841,41 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3901,17 +3901,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4014,14 +4014,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4044,33 +4044,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4160,14 +4160,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4199,24 +4199,24 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4306,14 +4306,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4345,11 +4345,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4379,14 +4379,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4417,10 +4417,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4429,41 +4427,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4495,11 +4491,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4529,14 +4525,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4559,7 +4555,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4567,8 +4563,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4577,39 +4575,41 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4641,11 +4641,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4675,14 +4675,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4716,9 +4716,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4748,14 +4748,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4781,17 +4781,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4821,14 +4821,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4894,14 +4894,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4924,33 +4924,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5040,14 +5040,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5070,33 +5070,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5186,14 +5186,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5216,33 +5216,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5332,14 +5332,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5371,24 +5371,24 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5405,14 +5405,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5443,10 +5443,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5455,41 +5453,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5515,17 +5511,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5555,14 +5551,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5585,7 +5581,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5593,8 +5589,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5603,39 +5601,41 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5658,33 +5658,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5701,14 +5701,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5742,9 +5742,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5774,14 +5774,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5804,33 +5804,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5847,14 +5847,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5880,17 +5880,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5920,14 +5920,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5950,33 +5950,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5993,14 +5993,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6023,12 +6023,12 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
@@ -6041,15 +6041,15 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6066,14 +6066,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6096,33 +6096,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6139,14 +6139,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6169,33 +6169,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6212,14 +6212,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6242,20 +6242,20 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6264,11 +6264,11 @@
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6285,14 +6285,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6315,33 +6315,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6358,14 +6358,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6388,25 +6388,25 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6431,14 +6431,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6470,24 +6470,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6504,14 +6504,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6539,20 +6539,20 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6577,14 +6577,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6616,11 +6616,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6650,14 +6650,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6689,24 +6689,24 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6723,14 +6723,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6762,11 +6762,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6796,14 +6796,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6835,11 +6835,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6869,14 +6869,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6902,17 +6902,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6942,14 +6942,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6981,11 +6981,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7015,14 +7015,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7045,12 +7045,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
@@ -7058,20 +7058,20 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7088,12 +7088,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7129,9 +7129,9 @@
       <c r="I91" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7161,14 +7161,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7191,7 +7191,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7209,15 +7209,15 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7234,14 +7234,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7273,11 +7273,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7307,14 +7307,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7340,17 +7340,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7380,14 +7380,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7413,17 +7413,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7453,14 +7453,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7483,33 +7483,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7526,14 +7526,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7556,33 +7556,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7599,14 +7599,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7638,24 +7638,24 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7672,14 +7672,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7711,24 +7711,24 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7745,14 +7745,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7784,11 +7784,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7818,14 +7818,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7851,17 +7851,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7891,14 +7891,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -7964,14 +7964,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7994,33 +7994,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8037,14 +8037,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8078,9 +8078,9 @@
       <c r="I104" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8110,14 +8110,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8149,24 +8149,24 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8183,14 +8183,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8222,11 +8222,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8256,14 +8256,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8295,11 +8295,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8329,14 +8329,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8362,17 +8362,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8402,14 +8402,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8441,11 +8441,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8475,14 +8475,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8505,16 +8505,16 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -8527,11 +8527,11 @@
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8548,14 +8548,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8581,17 +8581,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8621,14 +8621,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8662,9 +8662,9 @@
       <c r="I112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8673,11 +8673,11 @@
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8694,14 +8694,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8724,33 +8724,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8767,14 +8767,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8800,17 +8800,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8840,14 +8840,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8870,33 +8870,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8913,14 +8913,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8943,20 +8943,20 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8965,11 +8965,11 @@
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8986,14 +8986,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9025,24 +9025,24 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9059,14 +9059,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9098,24 +9098,24 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9132,14 +9132,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9171,11 +9171,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9278,14 +9278,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9317,11 +9317,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9351,14 +9351,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9390,7 +9390,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9424,14 +9424,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9457,17 +9457,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9497,14 +9497,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9538,9 +9538,9 @@
       <c r="I124" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9570,14 +9570,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9600,33 +9600,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9643,14 +9643,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9682,11 +9682,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9716,14 +9716,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9746,33 +9746,33 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9789,14 +9789,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9828,11 +9828,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9862,14 +9862,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -9903,22 +9903,22 @@
       <c r="I129" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9935,14 +9935,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9974,11 +9974,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
@@ -10008,14 +10008,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10047,11 +10047,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10081,14 +10081,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
@@ -10154,14 +10154,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10193,11 +10193,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10227,14 +10227,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10260,17 +10260,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10300,14 +10300,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10333,17 +10333,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10373,14 +10373,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10403,33 +10403,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10446,14 +10446,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10476,33 +10476,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10519,14 +10519,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10558,24 +10558,24 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10592,14 +10592,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10622,25 +10622,25 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10665,14 +10665,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10704,11 +10704,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10738,14 +10738,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10777,16 +10777,16 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
@@ -10811,14 +10811,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10850,11 +10850,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10884,14 +10884,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10917,22 +10917,22 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10957,14 +10957,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10996,11 +10996,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11030,14 +11030,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11060,25 +11060,25 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11103,14 +11103,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -11176,14 +11176,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11206,25 +11206,25 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11249,14 +11249,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11279,7 +11279,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -11287,10 +11287,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I148" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11299,41 +11297,39 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11356,7 +11352,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11365,24 +11361,24 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11399,14 +11395,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11429,7 +11425,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -11437,8 +11433,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I150" s="2" t="n">
-        <v>0</v>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
@@ -11447,39 +11445,41 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L150" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11505,17 +11505,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11545,14 +11545,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11586,9 +11586,9 @@
       <c r="I152" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11618,14 +11618,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11648,33 +11648,33 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11691,14 +11691,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11730,11 +11730,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11764,14 +11764,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11794,20 +11794,20 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11816,11 +11816,11 @@
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -11837,14 +11837,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11870,17 +11870,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11910,14 +11910,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11940,33 +11940,33 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -11983,14 +11983,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12013,33 +12013,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12056,14 +12056,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12086,33 +12086,33 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12129,14 +12129,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
@@ -12177,15 +12177,15 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12202,14 +12202,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12232,7 +12232,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12241,24 +12241,24 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12275,14 +12275,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12316,9 +12316,9 @@
       <c r="I162" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12348,12 +12348,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12389,9 +12389,9 @@
       <c r="I163" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12421,14 +12421,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12460,11 +12460,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12494,14 +12494,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12533,11 +12533,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12567,14 +12567,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12600,9 +12600,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12640,14 +12640,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12673,17 +12673,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12713,14 +12713,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12743,20 +12743,20 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12765,11 +12765,11 @@
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12786,14 +12786,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12816,33 +12816,33 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>2</v>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L169" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -12859,14 +12859,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12889,7 +12889,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -12898,24 +12898,24 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L170" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -12932,14 +12932,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12967,20 +12967,20 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L171" s="2" t="n">
@@ -13002,8 +13002,154 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 37,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>28</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 211,1%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,10 +743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -755,41 +753,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -815,13 +811,13 @@
           <t>R$ 37,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -830,7 +826,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -838,7 +834,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -855,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -885,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -893,8 +889,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -903,39 +901,41 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -958,33 +958,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 37,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1001,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1042,9 +1042,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1074,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1109,20 +1109,20 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 76,9%</t>
+        <v>16</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1147,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1186,11 +1186,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1220,14 +1220,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 74,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1259,24 +1259,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 85,7%</t>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1293,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1366,14 +1366,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1399,17 +1399,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1480,9 +1480,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1512,14 +1512,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1542,33 +1542,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 186,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 402,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1585,14 +1585,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1618,17 +1618,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1658,14 +1658,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1688,33 +1688,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 37,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,5%</t>
+          <t>R$ 186,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 402,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,14 +1731,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1761,33 +1761,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 37,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1804,14 +1804,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1834,25 +1834,25 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 37,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1877,14 +1877,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 37,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1916,24 +1916,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1950,14 +1950,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1989,24 +1989,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2023,14 +2023,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2062,11 +2062,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2096,14 +2096,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2135,11 +2135,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2242,14 +2242,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2281,11 +2281,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2388,14 +2388,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2421,9 +2421,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2461,14 +2461,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2499,10 +2499,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2511,41 +2509,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2568,20 +2564,20 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2590,11 +2586,11 @@
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2611,14 +2607,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2641,7 +2637,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2649,8 +2645,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2659,39 +2657,41 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2723,11 +2723,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2757,14 +2757,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2798,9 +2798,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2830,14 +2830,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2869,11 +2869,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2903,14 +2903,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,14 +2976,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3015,11 +3015,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3049,14 +3049,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3088,11 +3088,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3122,14 +3122,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3161,11 +3161,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3268,14 +3268,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3341,14 +3341,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3379,10 +3379,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3391,39 +3389,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3491,12 +3487,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3568,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3641,12 +3637,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3718,12 +3714,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3791,12 +3787,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3868,12 +3864,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3941,14 +3937,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -3971,7 +3967,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3979,8 +3975,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -3989,39 +3987,41 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4047,17 +4047,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4160,14 +4160,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4190,33 +4190,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4306,14 +4306,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4345,24 +4345,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4452,14 +4452,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4491,11 +4491,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4525,14 +4525,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4563,10 +4563,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4575,41 +4573,39 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4641,11 +4637,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4675,14 +4671,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4705,7 +4701,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4713,8 +4709,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4723,39 +4721,41 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4787,11 +4787,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4821,14 +4821,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4862,9 +4862,9 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4894,14 +4894,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -4927,17 +4927,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4967,14 +4967,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5006,11 +5006,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5040,14 +5040,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5070,33 +5070,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5186,14 +5186,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5216,33 +5216,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5332,14 +5332,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5362,33 +5362,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5478,14 +5478,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5517,24 +5517,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5551,14 +5551,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5589,10 +5589,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5601,41 +5599,39 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5661,17 +5657,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5701,14 +5697,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5731,7 +5727,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5739,8 +5735,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5749,39 +5747,41 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5804,33 +5804,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5847,14 +5847,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5888,9 +5888,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5920,14 +5920,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -5950,33 +5950,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5993,14 +5993,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6026,17 +6026,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6066,14 +6066,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6096,33 +6096,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6139,14 +6139,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6169,12 +6169,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
@@ -6187,15 +6187,15 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6212,14 +6212,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6242,33 +6242,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6285,14 +6285,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6315,33 +6315,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6358,14 +6358,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6388,20 +6388,20 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6410,11 +6410,11 @@
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6431,14 +6431,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6461,33 +6461,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6504,14 +6504,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6534,25 +6534,25 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6577,14 +6577,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6616,24 +6616,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6650,14 +6650,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6685,20 +6685,20 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -6723,14 +6723,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6762,11 +6762,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6796,14 +6796,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6835,24 +6835,24 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6869,14 +6869,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6908,11 +6908,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6942,14 +6942,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -6981,11 +6981,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7015,14 +7015,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7048,17 +7048,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7088,14 +7088,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7127,11 +7127,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7161,14 +7161,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7191,12 +7191,12 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
@@ -7204,20 +7204,20 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7275,9 +7275,9 @@
       <c r="I93" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7307,14 +7307,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7355,15 +7355,15 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7380,14 +7380,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7419,11 +7419,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7453,14 +7453,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7486,17 +7486,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7526,14 +7526,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7559,17 +7559,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7599,14 +7599,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7629,33 +7629,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7672,14 +7672,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7702,33 +7702,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7745,14 +7745,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7784,24 +7784,24 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7818,14 +7818,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7857,24 +7857,24 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7891,14 +7891,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7930,11 +7930,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7964,14 +7964,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -7997,17 +7997,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8037,14 +8037,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8110,14 +8110,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8140,33 +8140,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8183,14 +8183,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8224,9 +8224,9 @@
       <c r="I106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8256,14 +8256,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8295,24 +8295,24 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8329,14 +8329,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8368,11 +8368,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8402,14 +8402,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8441,11 +8441,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8475,14 +8475,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8508,17 +8508,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8548,14 +8548,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8587,11 +8587,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8621,14 +8621,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8651,16 +8651,16 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8673,11 +8673,11 @@
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8694,14 +8694,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8727,17 +8727,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8767,14 +8767,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8808,9 +8808,9 @@
       <c r="I114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8819,11 +8819,11 @@
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8840,14 +8840,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8870,33 +8870,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8913,14 +8913,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -8946,17 +8946,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8986,14 +8986,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9016,33 +9016,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9059,14 +9059,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9089,20 +9089,20 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9111,11 +9111,11 @@
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9132,14 +9132,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9171,24 +9171,24 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9205,14 +9205,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9235,7 +9235,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9244,24 +9244,24 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9278,14 +9278,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9317,11 +9317,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9424,14 +9424,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9463,11 +9463,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9497,14 +9497,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -9570,14 +9570,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9603,17 +9603,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9643,14 +9643,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9684,9 +9684,9 @@
       <c r="I126" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9716,14 +9716,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9746,33 +9746,33 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9789,14 +9789,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9828,11 +9828,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9862,14 +9862,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9892,33 +9892,33 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9935,14 +9935,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -9974,11 +9974,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10008,14 +10008,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10049,22 +10049,22 @@
       <c r="I131" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -10081,14 +10081,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10120,11 +10120,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
@@ -10154,14 +10154,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10193,11 +10193,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10227,14 +10227,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10266,7 +10266,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
@@ -10300,14 +10300,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10339,11 +10339,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10373,14 +10373,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10406,17 +10406,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10446,14 +10446,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10479,17 +10479,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10519,14 +10519,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10549,33 +10549,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10592,14 +10592,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10622,33 +10622,33 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10665,14 +10665,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -10704,24 +10704,24 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10738,14 +10738,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10768,25 +10768,25 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10811,14 +10811,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10850,11 +10850,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10884,14 +10884,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10923,16 +10923,16 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
@@ -10957,14 +10957,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -10996,11 +10996,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11030,14 +11030,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11063,22 +11063,22 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11103,14 +11103,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11142,11 +11142,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11176,14 +11176,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11206,25 +11206,25 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H147" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11249,14 +11249,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11322,14 +11322,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11352,25 +11352,25 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11395,14 +11395,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11425,7 +11425,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -11433,10 +11433,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I150" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
@@ -11445,41 +11443,39 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11502,7 +11498,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11511,24 +11507,24 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11545,14 +11541,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11575,7 +11571,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -11583,8 +11579,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I152" s="2" t="n">
-        <v>0</v>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -11593,39 +11591,41 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11651,17 +11651,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11691,14 +11691,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11732,9 +11732,9 @@
       <c r="I154" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11764,14 +11764,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11794,33 +11794,33 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -11837,14 +11837,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11876,11 +11876,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11910,14 +11910,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -11940,20 +11940,20 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -11962,11 +11962,11 @@
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -11983,14 +11983,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12016,17 +12016,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12056,14 +12056,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12086,33 +12086,33 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12129,14 +12129,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12159,33 +12159,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12202,14 +12202,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12232,33 +12232,33 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12275,14 +12275,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
@@ -12323,15 +12323,15 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12348,14 +12348,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12387,24 +12387,24 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12421,14 +12421,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12462,9 +12462,9 @@
       <c r="I164" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12494,12 +12494,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12535,9 +12535,9 @@
       <c r="I165" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12567,14 +12567,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12606,11 +12606,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12640,14 +12640,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12679,11 +12679,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12713,14 +12713,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12746,9 +12746,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12786,14 +12786,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12819,17 +12819,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12859,14 +12859,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12889,20 +12889,20 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12911,11 +12911,11 @@
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -12932,14 +12932,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -12962,33 +12962,33 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>2</v>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L171" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
@@ -13005,14 +13005,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -13044,24 +13044,24 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L172" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13078,14 +13078,14 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
           <t>UTD-002</t>
@@ -13113,20 +13113,20 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L173" s="2" t="n">
@@ -13148,8 +13148,154 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
+++ b/saida_skus/SKU_UTD-002-CABIDE-TRANSPARENTE.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 54,1%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 211,1%</t>
+        <v>6</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 37,00</t>
+          <t>R$ 74,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -889,51 +889,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -958,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 37,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1001,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1040,7 +1036,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1074,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1104,12 +1100,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
@@ -1117,20 +1113,20 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,4%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1147,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1188,9 +1184,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1220,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1250,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 74,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 76,9%</t>
+          <t>▲ 211,1%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1293,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1332,7 +1328,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1366,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1396,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 37,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1439,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1469,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1477,8 +1473,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1487,37 +1485,39 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1542,33 +1542,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 37,00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1626,9 +1626,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1688,33 +1688,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 186,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 402,7%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,4%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1764,17 +1764,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1834,33 +1834,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 37,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,5%</t>
+          <t>R$ 74,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▲ 76,9%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 37,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1916,24 +1916,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1989,24 +1989,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2062,11 +2062,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2208,11 +2208,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2272,33 +2272,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 186,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 402,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2348,17 +2348,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2418,33 +2418,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 37,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,5%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 37,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2500,24 +2500,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2564,33 +2564,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2645,51 +2645,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2714,7 +2710,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2723,11 +2719,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2736,11 +2732,11 @@
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2757,12 +2753,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2796,11 +2792,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2830,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2869,11 +2865,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2903,12 +2899,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2942,11 +2938,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,12 +2972,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3015,11 +3011,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3049,12 +3045,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3090,9 +3086,9 @@
       <c r="I36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3122,12 +3118,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3155,17 +3151,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3195,12 +3191,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3225,7 +3221,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3233,47 +3229,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>1</v>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3307,11 +3307,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3320,11 +3320,11 @@
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3341,12 +3341,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3414,12 +3414,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3453,11 +3453,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3487,12 +3487,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3525,51 +3525,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3603,11 +3599,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3637,12 +3633,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3667,7 +3663,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3675,51 +3671,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3753,11 +3745,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3787,12 +3779,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3817,7 +3809,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3825,51 +3817,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3903,7 +3891,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3937,12 +3925,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3967,7 +3955,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3975,10 +3963,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -3987,39 +3973,37 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4087,12 +4071,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4117,7 +4101,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4125,8 +4109,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4135,37 +4121,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4193,17 +4181,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4233,12 +4221,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4263,7 +4251,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4271,8 +4259,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4281,37 +4271,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4336,7 +4328,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4345,24 +4337,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4379,12 +4371,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4409,7 +4401,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4417,8 +4409,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4427,37 +4421,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4491,7 +4487,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4525,12 +4521,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4555,7 +4551,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4563,8 +4559,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4573,37 +4571,39 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4639,9 +4639,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4709,10 +4709,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4721,39 +4719,37 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4781,17 +4777,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4821,12 +4817,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4894,12 +4890,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4924,7 +4920,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4935,22 +4931,22 @@
       <c r="I61" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4967,12 +4963,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5008,9 +5004,9 @@
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5040,12 +5036,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5073,17 +5069,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5113,12 +5109,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5152,11 +5148,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5186,12 +5182,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5216,7 +5212,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5225,24 +5221,24 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5259,12 +5255,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5289,7 +5285,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5297,47 +5293,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>1</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5365,17 +5365,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5444,11 +5444,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5517,24 +5517,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5590,11 +5590,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5657,17 +5657,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5697,12 +5697,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5735,51 +5735,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I72" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5804,33 +5800,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5847,12 +5843,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5886,11 +5882,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5920,12 +5916,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5950,33 +5946,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5993,12 +5989,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6032,11 +6028,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6066,12 +6062,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6096,33 +6092,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6139,12 +6135,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6172,17 +6168,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6212,12 +6208,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6242,7 +6238,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6251,24 +6247,24 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6285,12 +6281,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6315,7 +6311,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6323,47 +6319,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>2</v>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6397,11 +6397,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6464,17 +6464,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6537,30 +6537,30 @@
           <t>R$ 72,00</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6616,24 +6616,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6650,12 +6650,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
@@ -6693,20 +6693,20 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6756,17 +6756,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6835,16 +6835,16 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
@@ -6869,12 +6869,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6912,20 +6912,20 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6975,17 +6975,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7048,17 +7048,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7088,12 +7088,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7118,33 +7118,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
@@ -7204,20 +7204,20 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7264,33 +7264,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7346,24 +7346,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7419,24 +7419,24 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7453,12 +7453,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7526,12 +7526,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7565,11 +7565,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7632,9 +7632,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
@@ -7672,12 +7672,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7705,17 +7705,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7745,12 +7745,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
@@ -7788,20 +7788,20 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7857,24 +7857,24 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7930,24 +7930,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8005,9 +8005,9 @@
       <c r="I103" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8110,12 +8110,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8143,17 +8143,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8183,12 +8183,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8216,17 +8216,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8286,33 +8286,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8329,12 +8329,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8368,24 +8368,24 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8441,24 +8441,24 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8514,11 +8514,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8587,11 +8587,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8621,12 +8621,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8654,9 +8654,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
@@ -8694,12 +8694,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8727,17 +8727,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8819,11 +8819,11 @@
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8870,33 +8870,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9016,33 +9016,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9059,12 +9059,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9092,17 +9092,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9132,12 +9132,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9171,24 +9171,24 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9235,20 +9235,20 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9257,11 +9257,11 @@
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9317,11 +9317,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9390,24 +9390,24 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9457,17 +9457,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9536,11 +9536,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9570,12 +9570,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9600,33 +9600,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9643,12 +9643,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9676,13 +9676,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -9716,12 +9716,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9746,33 +9746,33 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -9841,11 +9841,11 @@
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9892,33 +9892,33 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H129" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10047,24 +10047,24 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -10081,12 +10081,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10120,11 +10120,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10154,12 +10154,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10193,11 +10193,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>5</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10227,12 +10227,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10333,17 +10333,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10414,9 +10414,9 @@
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10476,33 +10476,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10552,17 +10552,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10592,12 +10592,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10622,33 +10622,33 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10665,12 +10665,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -10704,24 +10704,24 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10738,12 +10738,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10768,33 +10768,33 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H141" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10850,11 +10850,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
@@ -10884,12 +10884,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -10914,33 +10914,33 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11030,12 +11030,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11060,33 +11060,33 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11103,12 +11103,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11136,9 +11136,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
@@ -11176,12 +11176,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11206,33 +11206,33 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -11297,15 +11297,15 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11352,25 +11352,25 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11436,9 +11436,9 @@
       <c r="I150" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11468,12 +11468,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11503,20 +11503,20 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11541,12 +11541,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -11579,10 +11579,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I152" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -11591,39 +11589,37 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11648,12 +11644,12 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
@@ -11666,15 +11662,15 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11691,12 +11687,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11732,9 +11728,9 @@
       <c r="I154" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11764,12 +11760,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11794,33 +11790,33 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -11837,12 +11833,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11876,11 +11872,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11910,12 +11906,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -11940,33 +11936,33 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -11983,12 +11979,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12022,7 +12018,7 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
@@ -12056,12 +12052,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12095,16 +12091,16 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
@@ -12112,7 +12108,7 @@
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12129,12 +12125,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12159,55 +12155,59 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12235,17 +12235,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
@@ -12323,15 +12323,15 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12348,12 +12348,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12378,33 +12378,33 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12462,9 +12462,9 @@
       <c r="I164" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12494,12 +12494,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12524,33 +12524,33 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12567,12 +12567,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12606,11 +12606,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12679,24 +12679,24 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12713,12 +12713,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12746,17 +12746,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12786,12 +12786,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -12819,17 +12819,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12859,12 +12859,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -12889,33 +12889,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L170" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -12932,12 +12932,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -12962,33 +12962,33 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J171" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L171" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -13046,9 +13046,9 @@
       <c r="I172" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13057,11 +13057,11 @@
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13108,33 +13108,33 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I173" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J173" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
-        </is>
-      </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L173" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13190,11 +13190,11 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -13224,78 +13224,662 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4353289878</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-002</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Cabide Transparente</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>1835080889</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-002</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Cabide Transparente</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4353289878</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="n">
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
         <is>
           <t>12,5%</t>
         </is>
       </c>
-      <c r="L175" s="2" t="n">
+      <c r="L183" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M175" s="2" t="inlineStr">
+      <c r="M183" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="N183" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>